--- a/docs/legal-acts/export/EU 2016-679.xlsx
+++ b/docs/legal-acts/export/EU 2016-679.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 18:24</t>
+          <t>2026-10-21 18:31</t>
         </is>
       </c>
     </row>
@@ -16178,7 +16178,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -16829,7 +16829,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -18782,7 +18782,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -18875,7 +18875,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -19061,7 +19061,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -19247,7 +19247,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -19433,7 +19433,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -19619,7 +19619,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -20084,7 +20084,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -20363,7 +20363,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -20828,7 +20828,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -21107,7 +21107,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -22037,7 +22037,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -22409,7 +22409,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -22502,7 +22502,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -22595,7 +22595,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -22781,7 +22781,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -22967,7 +22967,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -23060,7 +23060,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -23339,7 +23339,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -23525,7 +23525,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -23711,7 +23711,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -23897,7 +23897,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -23990,7 +23990,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -24269,7 +24269,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -24362,7 +24362,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -24455,7 +24455,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -24641,7 +24641,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -24734,7 +24734,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -24920,7 +24920,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -25013,7 +25013,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -25199,7 +25199,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -25385,7 +25385,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -25478,7 +25478,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -25571,7 +25571,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -25757,7 +25757,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -25850,7 +25850,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -25943,7 +25943,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -26036,7 +26036,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -26129,7 +26129,7 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -26222,7 +26222,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -26408,7 +26408,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -26501,7 +26501,7 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -26687,7 +26687,7 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -26873,7 +26873,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -27059,7 +27059,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -27152,7 +27152,7 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -27245,7 +27245,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -27338,7 +27338,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -27431,7 +27431,7 @@
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -27617,7 +27617,7 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -27710,7 +27710,7 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -27803,7 +27803,7 @@
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -27989,7 +27989,7 @@
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -28082,7 +28082,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -28268,7 +28268,7 @@
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -28454,7 +28454,7 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -28547,7 +28547,7 @@
       </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -28640,7 +28640,7 @@
       </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -28919,7 +28919,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -29012,7 +29012,7 @@
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -29291,7 +29291,7 @@
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -29384,7 +29384,7 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -29477,7 +29477,7 @@
       </c>
       <c r="F318" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -29570,7 +29570,7 @@
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -29663,7 +29663,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -29849,7 +29849,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -29942,7 +29942,7 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -30035,7 +30035,7 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -30128,7 +30128,7 @@
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -30221,7 +30221,7 @@
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -30314,7 +30314,7 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -30407,7 +30407,7 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -30593,7 +30593,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="F331" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
@@ -30779,7 +30779,7 @@
       </c>
       <c r="F332" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G332" s="3" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
@@ -30965,7 +30965,7 @@
       </c>
       <c r="F334" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -31058,7 +31058,7 @@
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -31244,7 +31244,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -31430,7 +31430,7 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -31523,7 +31523,7 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -31616,7 +31616,7 @@
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -31709,7 +31709,7 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -31802,7 +31802,7 @@
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -31895,7 +31895,7 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -31988,7 +31988,7 @@
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
@@ -32081,7 +32081,7 @@
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -32174,7 +32174,7 @@
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -32267,7 +32267,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
@@ -32453,7 +32453,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -32546,7 +32546,7 @@
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -32732,7 +32732,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -32825,7 +32825,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -32918,7 +32918,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -33011,7 +33011,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -33104,7 +33104,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -33197,7 +33197,7 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -33290,7 +33290,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -33383,7 +33383,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -33662,7 +33662,7 @@
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -33848,7 +33848,7 @@
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G365" s="3" t="inlineStr">
@@ -33941,7 +33941,7 @@
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -34127,7 +34127,7 @@
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
@@ -34220,7 +34220,7 @@
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G369" s="3" t="inlineStr">
@@ -34313,7 +34313,7 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -34406,7 +34406,7 @@
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G371" s="3" t="inlineStr">
@@ -34499,7 +34499,7 @@
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -34592,7 +34592,7 @@
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G373" s="3" t="inlineStr">
@@ -34685,7 +34685,7 @@
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G375" s="3" t="inlineStr">
@@ -34871,7 +34871,7 @@
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
@@ -34964,7 +34964,7 @@
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G377" s="3" t="inlineStr">
@@ -35057,7 +35057,7 @@
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
@@ -35150,7 +35150,7 @@
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
@@ -35243,7 +35243,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -35336,7 +35336,7 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
@@ -35429,7 +35429,7 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -35522,7 +35522,7 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -35615,7 +35615,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -35708,7 +35708,7 @@
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
@@ -35987,7 +35987,7 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
@@ -36080,7 +36080,7 @@
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G389" s="3" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
@@ -36266,7 +36266,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -36359,7 +36359,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -36452,7 +36452,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -36545,7 +36545,7 @@
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -36638,7 +36638,7 @@
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G395" s="3" t="inlineStr">
@@ -36731,7 +36731,7 @@
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
@@ -36824,7 +36824,7 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -36917,7 +36917,7 @@
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
@@ -37010,7 +37010,7 @@
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G399" s="3" t="inlineStr">
@@ -37103,7 +37103,7 @@
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
@@ -37196,7 +37196,7 @@
       </c>
       <c r="F401" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G401" s="3" t="inlineStr">
@@ -37289,7 +37289,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
